--- a/data.xlsx
+++ b/data.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meera\Downloads\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A202D8BB-712F-4219-A5BF-925E131F8312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6215AB99-B641-457F-9514-07A405576378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Classes" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
